--- a/Result/profitability/2467.xlsx
+++ b/Result/profitability/2467.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>1.37375</v>
+        <v>1.7475</v>
       </c>
       <c r="N2" t="n">
-        <v>43.09999999999999</v>
+        <v>43.92</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3</v>
+        <v>1.64875</v>
       </c>
       <c r="N3" t="n">
-        <v>41.81125</v>
+        <v>42.67625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.19</v>
+        <v>1.57625</v>
       </c>
       <c r="N4" t="n">
-        <v>40.73374999999999</v>
+        <v>41.4525</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11875</v>
+        <v>1.45875</v>
       </c>
       <c r="N5" t="n">
-        <v>39.46375</v>
+        <v>40.33875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.95</v>
+        <v>1.28625</v>
       </c>
       <c r="N6" t="n">
-        <v>38.0575</v>
+        <v>38.625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8112499999999999</v>
+        <v>1.10625</v>
       </c>
       <c r="N7" t="n">
-        <v>36.735</v>
+        <v>37.31874999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6075</v>
+        <v>0.73625</v>
       </c>
       <c r="N8" t="n">
-        <v>35.45125</v>
+        <v>35.36375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2783</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1426</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1357</v>
+      </c>
+      <c r="F75" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>763</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>27.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>115</v>
+      </c>
+      <c r="J75" t="n">
+        <v>878</v>
+      </c>
+      <c r="K75" t="n">
+        <v>640</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.88125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>44.42749999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3366013071895424</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6999999999999957</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01414998989286431</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.985401459854014</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1675843907110366</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
